--- a/artfynd/A 50096-2023 artfynd.xlsx
+++ b/artfynd/A 50096-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50096-2023 artfynd.xlsx
+++ b/artfynd/A 50096-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,6 +921,126 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>106660362</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56298</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100045</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cygnus cygnus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skirasjön, Brevens bruk, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>532952</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6539565</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-02-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-02-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ove Sjöberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ove Sjöberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50096-2023 artfynd.xlsx
+++ b/artfynd/A 50096-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,40 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99831531</v>
+        <v>106660362</v>
       </c>
       <c r="B2" t="n">
-        <v>55981</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102964</v>
+        <v>100045</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532952.4344324643</v>
+        <v>532952</v>
       </c>
       <c r="R2" t="n">
-        <v>6539565.370644005</v>
+        <v>6539565</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,22 +748,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,32 +790,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99831491</v>
+        <v>106861258</v>
       </c>
       <c r="B3" t="n">
-        <v>55946</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102963</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,30 +820,30 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skirasjön, Brevens bruk, Nrk</t>
+          <t>Skira, Brevens bruk, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532952.4344324643</v>
+        <v>532956</v>
       </c>
       <c r="R3" t="n">
-        <v>6539565.370644005</v>
+        <v>6539545</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,22 +867,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
+          <t>2023-02-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
+          <t>2023-02-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,61 +909,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106660362</v>
+        <v>101157719</v>
       </c>
       <c r="B4" t="n">
-        <v>56323</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57942</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100045</v>
+        <v>102119</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skirasjön, Brevens bruk, Nrk</t>
+          <t>Skira, Brevens bruk, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532952</v>
+        <v>532956</v>
       </c>
       <c r="R4" t="n">
-        <v>6539565</v>
+        <v>6539545</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,22 +986,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-02-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-02-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,6 +1015,486 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>99831491</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57546</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102963</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skrattmås</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chroicocephalus ridibundus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skirasjön, Brevens bruk, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>532952</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6539565</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ove Sjöberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ove Sjöberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>101917625</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58463</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skira, Brevens bruk, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>532956</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6539545</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ove Sjöberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ove Sjöberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>99923695</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skira, Brevens bruk, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>532956</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6539545</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-04-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-04-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ove Sjöberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ove Sjöberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>107581471</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58649</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103057</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sävsparv</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Emberiza schoeniclus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skira, Brevens bruk, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>532956</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6539545</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-03-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-03-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ove Sjöberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ove Sjöberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50096-2023 artfynd.xlsx
+++ b/artfynd/A 50096-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106660362</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106861258</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101157719</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99831491</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,6 +1278,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101917625</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1372,6 +1402,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99923695</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1495,8 +1530,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107581471</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>